--- a/nr-add-cip/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:39+00:00</t>
+    <t>2026-02-02T15:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-cip/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5681" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5643" uniqueCount="923">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:16+00:00</t>
+    <t>2026-02-23T08:39:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -906,10 +906,7 @@
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
   </si>
   <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/eprescription/ValueSet/fr-inpatient-medication-code</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -948,15 +945,6 @@
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/eprescription/StructureDefinition/fr-medication-noncompound|https://interop.esante.gouv.fr/ig/fhir/eprescription/StructureDefinition/fr-medication-compound)
 </t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/eprescription/ValueSet/fr-medication-code</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -3204,12 +3192,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO153"/>
+  <dimension ref="A1:AO152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="13.8125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3232,7 +3220,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="68.9140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6584,26 +6572,24 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y29" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>280</v>
@@ -6621,30 +6607,30 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -6666,7 +6652,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>282</v>
@@ -6740,37 +6726,35 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -6785,16 +6769,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6820,11 +6804,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6842,7 +6828,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -6857,27 +6843,27 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6885,7 +6871,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
@@ -6897,19 +6883,19 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6959,10 +6945,10 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>91</v>
@@ -6974,27 +6960,27 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>232</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7005,7 +6991,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -7017,17 +7003,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -7076,13 +7060,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -7091,27 +7075,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7122,7 +7106,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -7134,13 +7118,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>156</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>157</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>158</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7191,31 +7175,31 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>159</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>160</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -7223,21 +7207,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -7249,15 +7233,17 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -7294,31 +7280,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -7338,21 +7324,23 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -7364,17 +7352,15 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>187</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -7411,16 +7397,16 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>164</v>
@@ -7444,7 +7430,7 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -7455,14 +7441,12 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C37" t="s" s="2">
         <v>328</v>
       </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>82</v>
       </c>
@@ -7480,18 +7464,20 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -7540,19 +7526,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>164</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -7561,7 +7547,7 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
@@ -7572,10 +7558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7598,16 +7584,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7633,13 +7619,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -7657,7 +7643,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7666,7 +7652,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7689,10 +7675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7715,16 +7701,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7750,13 +7736,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7760,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7795,7 +7781,7 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>134</v>
+        <v>346</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -7806,10 +7792,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7832,16 +7818,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7891,7 +7877,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7912,7 +7898,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7923,10 +7909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7934,7 +7920,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7949,17 +7935,15 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>156</v>
+        <v>353</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -8008,7 +7992,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -8023,27 +8007,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>134</v>
+        <v>358</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8066,13 +8050,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8123,7 +8107,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -8138,27 +8122,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8166,7 +8150,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -8178,16 +8162,16 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8238,7 +8222,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8253,16 +8237,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -8270,10 +8254,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8293,18 +8277,20 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>372</v>
+        <v>175</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -8329,13 +8315,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -8353,7 +8339,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8368,16 +8354,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -8385,10 +8371,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8408,20 +8394,18 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>175</v>
+        <v>383</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -8446,31 +8430,31 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8485,16 +8469,16 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -8502,10 +8486,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8516,7 +8500,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -8528,15 +8512,17 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>387</v>
+        <v>175</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8561,13 +8547,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -8585,13 +8571,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -8600,27 +8586,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8643,16 +8629,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8678,13 +8664,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8702,7 +8688,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8717,27 +8703,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>399</v>
+        <v>232</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8757,20 +8743,18 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8819,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8834,16 +8818,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8851,10 +8835,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8877,13 +8861,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>411</v>
+        <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8934,7 +8918,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8949,13 +8933,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8966,10 +8950,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8992,7 +8976,7 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>417</v>
@@ -9049,7 +9033,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -9064,13 +9048,13 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -9081,10 +9065,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9095,7 +9079,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -9107,16 +9091,18 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>420</v>
+        <v>215</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -9164,13 +9150,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -9179,13 +9165,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -9196,10 +9182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9219,21 +9205,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -9257,13 +9243,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -9281,7 +9267,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9296,13 +9282,13 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
@@ -9313,10 +9299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9327,7 +9313,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -9339,17 +9325,15 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>175</v>
+        <v>435</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9374,13 +9358,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -9398,13 +9382,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -9413,13 +9397,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -9430,10 +9414,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9456,13 +9440,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9513,7 +9497,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9528,13 +9512,13 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -9545,10 +9529,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9559,7 +9543,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9571,13 +9555,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>445</v>
+        <v>156</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>157</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9628,28 +9612,28 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>444</v>
+        <v>159</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>82</v>
@@ -9660,21 +9644,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9686,15 +9670,17 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9731,31 +9717,31 @@
         <v>82</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9775,21 +9761,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9801,16 +9789,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>451</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>187</v>
+        <v>452</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>188</v>
+        <v>453</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>189</v>
+        <v>454</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9848,16 +9836,16 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>164</v>
@@ -9881,7 +9869,7 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9892,14 +9880,12 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9917,19 +9903,19 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9979,19 +9965,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>164</v>
+        <v>460</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -10000,21 +9986,21 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10037,17 +10023,15 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>460</v>
+        <v>353</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -10096,7 +10080,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10117,7 +10101,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -10128,10 +10112,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10139,7 +10123,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
@@ -10154,13 +10138,13 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>357</v>
+        <v>468</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10211,10 +10195,10 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>91</v>
@@ -10232,7 +10216,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -10243,10 +10227,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10257,7 +10241,7 @@
         <v>91</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -10266,18 +10250,20 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -10326,13 +10312,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -10341,27 +10327,27 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10369,10 +10355,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -10384,17 +10370,15 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>478</v>
+        <v>156</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>479</v>
+        <v>157</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -10443,28 +10427,28 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>159</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>483</v>
+        <v>160</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -10475,21 +10459,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10501,15 +10485,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10546,31 +10532,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10590,14 +10576,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10610,24 +10596,26 @@
         <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>187</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>188</v>
+        <v>485</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10663,19 +10651,19 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10696,7 +10684,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -10707,45 +10695,43 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>488</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>212</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10794,19 +10780,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10815,21 +10801,21 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>134</v>
+        <v>493</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10852,17 +10838,17 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>492</v>
+        <v>156</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10911,7 +10897,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10932,21 +10918,21 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10957,7 +10943,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10969,17 +10955,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -11004,13 +10992,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -11028,13 +11016,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -11049,21 +11037,21 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11074,7 +11062,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -11086,20 +11074,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -11123,13 +11107,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -11147,13 +11131,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -11168,13 +11152,13 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="69">
@@ -11193,7 +11177,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -11205,16 +11189,20 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>156</v>
+        <v>515</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11262,7 +11250,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11283,21 +11271,21 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11317,23 +11305,19 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>156</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>157</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11381,7 +11365,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>159</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11393,7 +11377,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -11402,7 +11386,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -11413,21 +11397,21 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -11439,15 +11423,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11484,31 +11470,31 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11528,14 +11514,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11548,24 +11534,26 @@
         <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>187</v>
+        <v>484</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>188</v>
+        <v>485</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11601,19 +11589,19 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11634,7 +11622,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -11645,14 +11633,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11665,25 +11653,23 @@
         <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>136</v>
+        <v>353</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>212</v>
+        <v>528</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11732,7 +11718,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11744,7 +11730,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11753,7 +11739,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>134</v>
+        <v>530</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11764,10 +11750,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11778,7 +11764,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11790,17 +11776,17 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>357</v>
+        <v>532</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11849,19 +11835,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>103</v>
+        <v>537</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11870,7 +11856,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11881,10 +11867,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11904,21 +11890,19 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>536</v>
+        <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>157</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>538</v>
+        <v>158</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>539</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11966,7 +11950,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>540</v>
+        <v>159</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11978,7 +11962,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11987,7 +11971,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>542</v>
+        <v>160</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11998,21 +11982,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -12024,15 +12008,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -12069,31 +12055,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -12113,21 +12099,23 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="D77" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -12139,17 +12127,15 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>136</v>
+        <v>543</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>187</v>
+        <v>544</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -12186,16 +12172,16 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>164</v>
@@ -12219,7 +12205,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -12230,14 +12216,12 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C78" t="s" s="2">
         <v>546</v>
       </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -12255,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>547</v>
@@ -12315,19 +12299,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>164</v>
+        <v>550</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -12336,7 +12320,7 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -12347,10 +12331,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12373,16 +12357,20 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -12430,7 +12418,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12451,7 +12439,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -12462,10 +12450,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12488,20 +12476,16 @@
         <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12549,7 +12533,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12570,7 +12554,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -12607,16 +12591,20 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12664,7 +12652,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12685,7 +12673,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -12696,10 +12684,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12722,19 +12710,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O82" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12783,7 +12771,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12804,7 +12792,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12841,7 +12829,7 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>569</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>577</v>
@@ -12849,12 +12837,8 @@
       <c r="M83" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N83" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>573</v>
-      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12878,13 +12862,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12902,7 +12886,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12923,7 +12907,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12934,10 +12918,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12960,20 +12944,22 @@
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>553</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q84" s="2"/>
+      <c r="Q84" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="R84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12993,13 +12979,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -13017,7 +13003,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13038,7 +13024,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -13049,10 +13035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13075,22 +13061,20 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q85" t="s" s="2">
-        <v>590</v>
-      </c>
+      <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
         <v>82</v>
       </c>
@@ -13155,7 +13139,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -13192,13 +13176,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13249,7 +13233,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13270,7 +13254,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13265,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13307,10 +13291,10 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>597</v>
@@ -13385,7 +13369,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -13422,13 +13406,13 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>569</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13455,13 +13439,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13479,7 +13463,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13500,7 +13484,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -13511,10 +13495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13525,7 +13509,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -13540,12 +13524,14 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13572,11 +13558,9 @@
       <c r="X89" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Y89" t="s" s="2">
-        <v>583</v>
-      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13594,13 +13578,13 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
@@ -13615,7 +13599,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>586</v>
+        <v>160</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -13626,10 +13610,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13652,16 +13636,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>609</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13687,11 +13671,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13709,7 +13695,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13741,10 +13727,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13767,18 +13753,20 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>613</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13802,13 +13790,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13826,7 +13814,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13847,7 +13835,7 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>160</v>
+        <v>622</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
@@ -13858,10 +13846,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13872,7 +13860,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13884,20 +13872,16 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>624</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13921,13 +13905,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13945,13 +13929,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13966,7 +13950,7 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
@@ -13977,10 +13961,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14003,15 +13987,17 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>628</v>
+        <v>175</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -14036,13 +14022,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -14060,7 +14046,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14081,7 +14067,7 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
@@ -14092,10 +14078,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14118,16 +14104,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>175</v>
+        <v>638</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14153,13 +14139,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -14177,7 +14163,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14198,21 +14184,21 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14235,18 +14221,20 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>642</v>
+        <v>175</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -14273,10 +14261,10 @@
         <v>239</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -14294,7 +14282,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14315,21 +14303,21 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14355,16 +14343,14 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>654</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14389,13 +14375,11 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>656</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14413,7 +14397,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14434,21 +14418,21 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14474,14 +14458,16 @@
         <v>175</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="O97" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14510,7 +14496,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14528,7 +14514,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14549,21 +14535,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14574,7 +14560,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14586,20 +14572,16 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>175</v>
+        <v>532</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>673</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14623,11 +14605,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14645,13 +14629,13 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
@@ -14666,21 +14650,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>676</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14691,7 +14675,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14700,16 +14684,16 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>536</v>
+        <v>156</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>679</v>
+        <v>157</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14760,19 +14744,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>681</v>
+        <v>159</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14781,32 +14765,32 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14818,15 +14802,17 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14863,31 +14849,31 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14907,21 +14893,23 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="D101" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14933,17 +14921,15 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>683</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>187</v>
+        <v>684</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14980,16 +14966,16 @@
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>164</v>
@@ -15013,7 +14999,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -15024,14 +15010,12 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C102" t="s" s="2">
         <v>686</v>
       </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>82</v>
       </c>
@@ -15049,19 +15033,21 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -15085,13 +15071,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>690</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -15109,19 +15095,19 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>164</v>
+        <v>692</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -15136,15 +15122,15 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>693</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15167,17 +15153,19 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>175</v>
+        <v>695</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>697</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15202,31 +15190,29 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>694</v>
+        <v>82</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15247,23 +15233,25 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>82</v>
+        <v>672</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="D104" t="s" s="2">
         <v>82</v>
       </c>
@@ -15284,19 +15272,19 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15333,17 +15321,19 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15364,24 +15354,24 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>82</v>
@@ -15403,19 +15393,19 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15464,7 +15454,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15485,25 +15475,23 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15524,19 +15512,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L106" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>701</v>
-      </c>
       <c r="N106" t="s" s="2">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15573,19 +15561,17 @@
         <v>82</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15606,23 +15592,25 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>676</v>
+        <v>715</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15643,19 +15631,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15692,17 +15680,19 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15723,13 +15713,13 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="108">
@@ -15737,7 +15727,7 @@
         <v>721</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>722</v>
@@ -15762,19 +15752,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15823,7 +15813,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15844,24 +15834,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>82</v>
@@ -15883,19 +15873,19 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15944,7 +15934,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15965,25 +15955,23 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>728</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>82</v>
       </c>
@@ -16004,19 +15992,19 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -16065,7 +16053,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16086,21 +16074,21 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>720</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16120,23 +16108,19 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>730</v>
+        <v>156</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>731</v>
+        <v>157</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>734</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -16184,7 +16168,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>735</v>
+        <v>159</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16196,7 +16180,7 @@
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -16205,32 +16189,32 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>736</v>
+        <v>160</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>737</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -16242,15 +16226,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16287,31 +16273,31 @@
         <v>82</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16331,21 +16317,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
@@ -16354,20 +16340,18 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>136</v>
+        <v>707</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>187</v>
+        <v>737</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16404,31 +16388,31 @@
         <v>82</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>164</v>
+        <v>739</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16437,7 +16421,7 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>160</v>
+        <v>740</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>82</v>
@@ -16448,10 +16432,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16474,13 +16458,13 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16531,7 +16515,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16552,7 +16536,7 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
@@ -16563,10 +16547,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16589,16 +16573,20 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>748</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>750</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16646,7 +16634,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16667,7 +16655,7 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
@@ -16678,10 +16666,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16704,19 +16692,17 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>753</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16765,7 +16751,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16786,7 +16772,7 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
@@ -16797,10 +16783,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16820,21 +16806,19 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>760</v>
-      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16882,7 +16866,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16900,10 +16884,10 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>762</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16914,10 +16898,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16940,13 +16924,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>763</v>
+        <v>156</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>764</v>
+        <v>157</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>765</v>
+        <v>158</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16997,7 +16981,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>762</v>
+        <v>159</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17009,16 +16993,16 @@
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>766</v>
+        <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>767</v>
+        <v>160</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -17029,21 +17013,21 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>82</v>
@@ -17055,15 +17039,17 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -17112,19 +17098,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -17144,14 +17130,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17164,24 +17150,26 @@
         <v>82</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>187</v>
+        <v>484</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>188</v>
+        <v>485</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17229,7 +17217,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17250,7 +17238,7 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>82</v>
@@ -17261,46 +17249,44 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>136</v>
+        <v>759</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>488</v>
+        <v>768</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>489</v>
+        <v>769</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17348,19 +17334,19 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>490</v>
+        <v>767</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17369,7 +17355,7 @@
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>134</v>
+        <v>771</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17380,10 +17366,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17406,17 +17392,15 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>763</v>
+        <v>156</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>772</v>
+        <v>157</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>774</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17465,7 +17449,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>771</v>
+        <v>159</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17477,7 +17461,7 @@
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17486,7 +17470,7 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>775</v>
+        <v>160</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -17497,21 +17481,21 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -17523,15 +17507,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -17580,19 +17566,19 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>82</v>
@@ -17612,14 +17598,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -17632,24 +17618,26 @@
         <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>187</v>
+        <v>484</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>188</v>
+        <v>485</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O124" s="2"/>
+      <c r="O124" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17697,7 +17685,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17718,7 +17706,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17729,46 +17717,42 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>136</v>
+        <v>776</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>488</v>
+        <v>777</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>778</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17816,19 +17800,19 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>490</v>
+        <v>775</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>82</v>
@@ -17837,7 +17821,7 @@
         <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>134</v>
+        <v>779</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17848,10 +17832,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17874,13 +17858,13 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17931,7 +17915,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17952,7 +17936,7 @@
         <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17963,10 +17947,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17977,7 +17961,7 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
@@ -17989,7 +17973,7 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>786</v>
@@ -18046,7 +18030,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18067,7 +18051,7 @@
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -18078,10 +18062,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18092,7 +18076,7 @@
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
@@ -18104,7 +18088,7 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>790</v>
@@ -18112,8 +18096,12 @@
       <c r="M128" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+      <c r="N128" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>793</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -18161,7 +18149,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18179,10 +18167,10 @@
         <v>82</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>82</v>
+        <v>794</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -18193,10 +18181,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18219,20 +18207,16 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>793</v>
+        <v>156</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>794</v>
+        <v>157</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>797</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18280,7 +18264,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>792</v>
+        <v>159</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18292,16 +18276,16 @@
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>798</v>
+        <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>799</v>
+        <v>160</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18312,21 +18296,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>82</v>
@@ -18338,15 +18322,17 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18383,31 +18369,31 @@
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18427,21 +18413,21 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>82</v>
@@ -18450,19 +18436,19 @@
         <v>82</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>136</v>
+        <v>353</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>187</v>
+        <v>799</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>188</v>
+        <v>800</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>189</v>
+        <v>801</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18500,31 +18486,31 @@
         <v>82</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>164</v>
+        <v>802</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>82</v>
+        <v>803</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>82</v>
@@ -18533,21 +18519,21 @@
         <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>160</v>
+        <v>804</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>82</v>
+        <v>805</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18555,7 +18541,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>91</v>
@@ -18570,22 +18556,24 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q132" s="2"/>
+      <c r="Q132" t="s" s="2">
+        <v>810</v>
+      </c>
       <c r="R132" t="s" s="2">
         <v>82</v>
       </c>
@@ -18629,7 +18617,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18638,7 +18626,7 @@
         <v>91</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>103</v>
@@ -18650,21 +18638,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18684,72 +18672,70 @@
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>357</v>
+        <v>624</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q133" t="s" s="2">
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF133" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="R133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>815</v>
-      </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
@@ -18757,7 +18743,7 @@
         <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>807</v>
+        <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>103</v>
@@ -18766,24 +18752,24 @@
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>82</v>
+        <v>818</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18794,7 +18780,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18806,17 +18792,15 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>628</v>
+        <v>776</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>821</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18865,7 +18849,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18883,24 +18867,24 @@
         <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18911,7 +18895,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18923,15 +18907,17 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>829</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>830</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18980,7 +18966,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18998,24 +18984,24 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>830</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19038,17 +19024,15 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>785</v>
+        <v>156</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>832</v>
+        <v>157</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>834</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -19097,7 +19081,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>831</v>
+        <v>159</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19109,16 +19093,16 @@
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>835</v>
+        <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>836</v>
+        <v>160</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -19129,21 +19113,21 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
@@ -19155,15 +19139,17 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19200,31 +19186,31 @@
         <v>82</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>82</v>
@@ -19244,21 +19230,21 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -19267,21 +19253,23 @@
         <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>136</v>
+        <v>565</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>187</v>
+        <v>836</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>188</v>
+        <v>837</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O138" s="2"/>
+        <v>838</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>839</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19317,31 +19305,31 @@
         <v>82</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>164</v>
+        <v>840</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>82</v>
@@ -19350,21 +19338,21 @@
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>160</v>
+        <v>841</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>82</v>
+        <v>842</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19375,36 +19363,36 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>569</v>
+        <v>111</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>842</v>
-      </c>
+        <v>845</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q139" s="2"/>
+      <c r="Q139" t="s" s="2">
+        <v>847</v>
+      </c>
       <c r="R139" t="s" s="2">
         <v>82</v>
       </c>
@@ -19424,13 +19412,13 @@
         <v>82</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>82</v>
+        <v>848</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>82</v>
+        <v>849</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19448,7 +19436,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19469,21 +19457,21 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19494,36 +19482,34 @@
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q140" t="s" s="2">
-        <v>851</v>
-      </c>
+      <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
         <v>82</v>
       </c>
@@ -19543,13 +19529,13 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>852</v>
+        <v>82</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>853</v>
+        <v>82</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19567,7 +19553,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19588,21 +19574,21 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19625,17 +19611,17 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19684,7 +19670,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19693,7 +19679,7 @@
         <v>91</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>82</v>
+        <v>865</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>103</v>
@@ -19705,21 +19691,21 @@
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19742,17 +19728,19 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="O142" t="s" s="2">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19801,7 +19789,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19810,7 +19798,7 @@
         <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>869</v>
+        <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>103</v>
@@ -19822,21 +19810,21 @@
         <v>82</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19847,7 +19835,7 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>82</v>
@@ -19856,23 +19844,19 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>111</v>
+        <v>875</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>875</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19920,7 +19904,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19941,21 +19925,21 @@
         <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>863</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19966,7 +19950,7 @@
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>82</v>
@@ -19978,7 +19962,7 @@
         <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>879</v>
+        <v>759</v>
       </c>
       <c r="L144" t="s" s="2">
         <v>880</v>
@@ -20035,7 +20019,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20053,13 +20037,13 @@
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>82</v>
+        <v>882</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -20067,10 +20051,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20093,13 +20077,13 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>763</v>
+        <v>156</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>884</v>
+        <v>157</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>885</v>
+        <v>158</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20150,7 +20134,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>883</v>
+        <v>159</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20162,16 +20146,16 @@
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>886</v>
+        <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>887</v>
+        <v>160</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
@@ -20182,21 +20166,21 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>82</v>
@@ -20208,15 +20192,17 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20265,19 +20251,19 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>82</v>
@@ -20297,14 +20283,14 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20317,24 +20303,26 @@
         <v>82</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>187</v>
+        <v>484</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>188</v>
+        <v>485</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O147" s="2"/>
+      <c r="O147" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20382,7 +20370,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20403,7 +20391,7 @@
         <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
@@ -20414,46 +20402,44 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>136</v>
+        <v>638</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>488</v>
+        <v>888</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>489</v>
+        <v>889</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>890</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>82</v>
       </c>
@@ -20477,13 +20463,13 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>82</v>
+        <v>891</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>82</v>
+        <v>892</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20501,42 +20487,42 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>490</v>
+        <v>887</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>82</v>
+        <v>882</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>134</v>
+        <v>893</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>82</v>
+        <v>894</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20544,7 +20530,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>91</v>
@@ -20559,17 +20545,15 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>642</v>
+        <v>175</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>894</v>
-      </c>
+        <v>897</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20597,31 +20581,31 @@
         <v>239</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF149" t="s" s="2">
         <v>895</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>891</v>
-      </c>
       <c r="AG149" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>91</v>
@@ -20636,24 +20620,24 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20676,13 +20660,13 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>175</v>
+        <v>904</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20709,31 +20693,31 @@
         <v>82</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>902</v>
+        <v>82</v>
       </c>
       <c r="Z150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20748,38 +20732,38 @@
         <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>82</v>
+        <v>907</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>906</v>
+        <v>82</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>82</v>
+        <v>910</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>82</v>
@@ -20791,15 +20775,17 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>913</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>914</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20848,13 +20834,13 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
@@ -20863,13 +20849,13 @@
         <v>103</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>911</v>
+        <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>904</v>
+        <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20880,14 +20866,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>914</v>
+        <v>82</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20906,16 +20892,16 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20965,7 +20951,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20980,135 +20966,18 @@
         <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>82</v>
+        <v>921</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>922</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>924</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO153" t="s" s="2">
         <v>82</v>
       </c>
     </row>
